--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N161_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N161_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>52.63414455805892</v>
+        <v>8.553048490684574</v>
       </c>
       <c r="D2" t="n">
-        <v>32.86373757452834</v>
+        <v>5.340357355860855</v>
       </c>
       <c r="E2" t="n">
-        <v>14.97367047596756</v>
+        <v>2.433221452344729</v>
       </c>
       <c r="F2" t="n">
-        <v>7.085250647580898</v>
+        <v>1.151353230231896</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>8.986179460952018</v>
+        <v>1.460254162404703</v>
       </c>
       <c r="D3" t="n">
-        <v>8.690043410241497</v>
+        <v>1.412132054164243</v>
       </c>
       <c r="E3" t="n">
-        <v>14.97367047596756</v>
+        <v>2.433221452344729</v>
       </c>
       <c r="F3" t="n">
-        <v>7.085250647580898</v>
+        <v>1.151353230231896</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>16.41913646548245</v>
+        <v>2.668109675640898</v>
       </c>
       <c r="D4" t="n">
-        <v>21.39109541717229</v>
+        <v>3.476053005290497</v>
       </c>
       <c r="E4" t="n">
-        <v>14.97367047596756</v>
+        <v>2.433221452344729</v>
       </c>
       <c r="F4" t="n">
-        <v>7.085250647580898</v>
+        <v>1.151353230231896</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>50.04067487644281</v>
+        <v>8.131609667421957</v>
       </c>
       <c r="D5" t="n">
-        <v>20.05696290902509</v>
+        <v>3.259256472716578</v>
       </c>
       <c r="E5" t="n">
-        <v>14.97367047596756</v>
+        <v>2.433221452344729</v>
       </c>
       <c r="F5" t="n">
-        <v>7.085250647580898</v>
+        <v>1.151353230231896</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>19.29506109645806</v>
+        <v>3.135447428174435</v>
       </c>
       <c r="D6" t="n">
-        <v>16.93814690659524</v>
+        <v>2.752448872321726</v>
       </c>
       <c r="E6" t="n">
-        <v>14.97367047596756</v>
+        <v>2.433221452344729</v>
       </c>
       <c r="F6" t="n">
-        <v>7.085250647580898</v>
+        <v>1.151353230231896</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>27.02610763367823</v>
+        <v>4.391742490472712</v>
       </c>
       <c r="D7" t="n">
-        <v>9.996581926838838</v>
+        <v>1.624444563111311</v>
       </c>
       <c r="E7" t="n">
-        <v>14.97367047596756</v>
+        <v>2.433221452344729</v>
       </c>
       <c r="F7" t="n">
-        <v>7.085250647580898</v>
+        <v>1.151353230231896</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>44.50358313812441</v>
+        <v>7.231832259945216</v>
       </c>
       <c r="D8" t="n">
-        <v>9.160909513849569</v>
+        <v>1.488647796000555</v>
       </c>
       <c r="E8" t="n">
-        <v>14.97367047596756</v>
+        <v>2.433221452344729</v>
       </c>
       <c r="F8" t="n">
-        <v>7.085250647580898</v>
+        <v>1.151353230231896</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>43.17528156563203</v>
+        <v>7.015983254415205</v>
       </c>
       <c r="D9" t="n">
-        <v>17.12357806574052</v>
+        <v>2.782581435682835</v>
       </c>
       <c r="E9" t="n">
-        <v>14.97367047596756</v>
+        <v>2.433221452344729</v>
       </c>
       <c r="F9" t="n">
-        <v>7.085250647580898</v>
+        <v>1.151353230231896</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>35.04776511287938</v>
+        <v>5.6952618308429</v>
       </c>
       <c r="D10" t="n">
-        <v>23.69145759068869</v>
+        <v>3.849861858486912</v>
       </c>
       <c r="E10" t="n">
-        <v>14.97367047596756</v>
+        <v>2.433221452344729</v>
       </c>
       <c r="F10" t="n">
-        <v>7.085250647580898</v>
+        <v>1.151353230231896</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>16.31217952951372</v>
+        <v>2.650729173545979</v>
       </c>
       <c r="D11" t="n">
-        <v>16.04153968780913</v>
+        <v>2.606750199268984</v>
       </c>
       <c r="E11" t="n">
-        <v>14.97367047596756</v>
+        <v>2.433221452344729</v>
       </c>
       <c r="F11" t="n">
-        <v>7.085250647580898</v>
+        <v>1.151353230231896</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
